--- a/laporan_padel_dki_jakarta_2026-10-23.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-23.xlsx
@@ -739,7 +739,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.114.994</t>
+          <t>Rp4.436.994</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>136</v>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp13.640.000</t>
+          <t>Rp13.940.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.325.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp1.740.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp4.536.000</t>
+          <t>Rp3.696.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp6.760.000</t>
+          <t>Rp6.860.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.540.000</t>
+          <t>Rp7.510.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.296.000</t>
+          <t>Rp2.696.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp9.405.000</t>
+          <t>Rp11.025.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp1.894.000</t>
+          <t>Rp2.193.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp25.600.000</t>
+          <t>Rp25.775.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.481.000</t>
+          <t>Rp5.751.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.388.000</t>
+          <t>Rp6.566.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.840.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.885.000</t>
+          <t>Rp19.525.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.600.000</t>
+          <t>Rp10.850.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp5.150.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.420.000</t>
+          <t>Rp3.140.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.165.000</t>
+          <t>Rp10.765.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.465.000</t>
+          <t>Rp6.627.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.560.000</t>
+          <t>Rp5.160.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp16.600.000</t>
+          <t>Rp17.000.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp28.525.000</t>
+          <t>Rp28.825.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.840.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.105.000</t>
+          <t>Rp3.885.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.690.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.630.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.765.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp3.023.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-23.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-23.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp2.301.000</t>
+          <t>Rp2.598.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.244.000</t>
+          <t>Rp1.514.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.280.000</t>
+          <t>Rp5.760.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.885.000</t>
+          <t>Rp9.350.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.871.000</t>
+          <t>Rp15.146.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.770.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.075.000</t>
+          <t>Rp11.350.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.325.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.740.000</t>
+          <t>Rp1.365.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>16</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp400.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.785.000</t>
+          <t>Rp5.795.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.380.000</t>
+          <t>Rp6.176.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.744.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>30</v>
       </c>
       <c r="D53" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp120.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>18</v>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp595.000</t>
+          <t>Rp915.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.732.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.931.000</t>
+          <t>Rp6.431.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.715.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp3.430.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp6.045.000</t>
+          <t>Rp5.655.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.569.000</t>
+          <t>Rp4.867.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp2.388.000</t>
+          <t>Rp3.135.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp4.860.000</t>
+          <t>Rp4.940.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp495.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.680.000</t>
+          <t>Rp6.660.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp2.610.000</t>
+          <t>Rp3.130.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.134.000</t>
+          <t>Rp5.834.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.024.000</t>
+          <t>Rp1.374.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.696.000</t>
+          <t>Rp2.996.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp2.193.000</t>
+          <t>Rp2.393.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp25.775.000</t>
+          <t>Rp26.280.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp7.575.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp23.550.000</t>
+          <t>Rp23.700.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.825.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp835.000</t>
+          <t>Rp1.235.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp8.700.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp5.725.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.725.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>68</v>
       </c>
       <c r="D55" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp7.940.000</t>
+          <t>Rp8.215.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp195.000</t>
+          <t>Rp408.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>124</v>
       </c>
       <c r="D59" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.751.000</t>
+          <t>Rp6.345.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.566.000</t>
+          <t>Rp6.266.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.235.000</t>
+          <t>Rp8.935.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5741,16 +5741,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp13.000.000</t>
+          <t>Rp13.450.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp35.950.000</t>
+          <t>Rp39.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.150.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.630.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.070.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.890.000</t>
+          <t>Rp10.830.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.160.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.585.000</t>
+          <t>Rp15.165.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.900.000</t>
+          <t>Rp9.372.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.431.500</t>
+          <t>Rp19.711.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.626.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>72</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.240.000</t>
+          <t>Rp5.390.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.625.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp5.075.000</t>
+          <t>Rp4.875.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.335.000</t>
+          <t>Rp3.873.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.600.000</t>
+          <t>Rp22.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.627.000</t>
+          <t>Rp6.303.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.160.000</t>
+          <t>Rp6.180.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.040.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.982.000</t>
+          <t>Rp4.279.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.045.000</t>
+          <t>Rp9.290.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.000.000</t>
+          <t>Rp17.650.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7920,16 +7920,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.115.000</t>
+          <t>Rp10.645.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>174</v>
       </c>
       <c r="D46" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp27.300.000</t>
+          <t>Rp28.500.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8013,16 +8013,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.940.000</t>
+          <t>Rp7.190.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8137,16 +8137,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp470.000</t>
+          <t>Rp805.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.860.000</t>
+          <t>Rp11.760.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8340,14 +8340,14 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp20.430.000</t>
+          <t>Rp20.730.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.549.991</t>
+          <t>Rp4.924.991</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.890.000</t>
+          <t>Rp2.035.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.050.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -9189,12 +9189,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.070.000</t>
+          <t>Rp2.692.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp345.000</t>
+          <t>Rp150.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -9211,16 +9211,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.170.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.745.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9335,16 +9335,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.023.000</t>
+          <t>Rp3.173.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9366,16 +9366,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.595.000</t>
+          <t>Rp3.745.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9459,16 +9459,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp439.000</t>
+          <t>Rp679.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-23.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-23.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.360.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.000.000</t>
+          <t>Rp11.450.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.094.000</t>
+          <t>Rp2.694.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.146.000</t>
+          <t>Rp14.890.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.770.000</t>
+          <t>Rp2.945.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp11.350.000</t>
+          <t>Rp12.346.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.365.000</t>
+          <t>Rp440.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp376.000</t>
+          <t>Rp752.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.968.000</t>
+          <t>Rp3.038.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.916.000</t>
+          <t>Rp2.718.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.430.000</t>
+          <t>Rp4.890.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.744.000</t>
+          <t>Rp3.940.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.795.000</t>
+          <t>Rp5.415.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>68</v>
       </c>
       <c r="D40" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.190.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.176.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.220.000</t>
+          <t>Rp10.420.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>60</v>
       </c>
       <c r="D46" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp3.696.000</t>
+          <t>Rp3.276.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>54</v>
       </c>
       <c r="D48" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.490.000</t>
+          <t>Rp1.890.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.744.000</t>
+          <t>Rp5.184.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp120.000</t>
+          <t>Rp240.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp6.860.000</t>
+          <t>Rp7.080.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.494.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.430.000</t>
+          <t>Rp2.910.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp5.655.000</t>
+          <t>Rp6.045.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>126</v>
       </c>
       <c r="D81" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.867.000</t>
+          <t>Rp5.216.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp3.135.000</t>
+          <t>Rp3.235.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp4.940.000</t>
+          <t>Rp5.120.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>80</v>
       </c>
       <c r="D96" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp6.660.000</t>
+          <t>Rp6.909.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.470.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp3.130.000</t>
+          <t>Rp3.330.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.510.000</t>
+          <t>Rp8.060.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.374.000</t>
+          <t>Rp1.549.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.695.000</t>
+          <t>Rp4.395.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.996.000</t>
+          <t>Rp3.196.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp11.025.000</t>
+          <t>Rp11.835.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.475.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.940.000</t>
+          <t>Rp3.135.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp7.125.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.235.000</t>
+          <t>Rp2.020.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp6.799.000</t>
+          <t>Rp7.099.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>48</v>
       </c>
       <c r="D42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4935,16 +4935,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>80</v>
       </c>
       <c r="D49" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.725.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>72</v>
       </c>
       <c r="D51" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp3.168.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>54</v>
       </c>
       <c r="D52" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>75</v>
       </c>
       <c r="D57" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp408.000</t>
+          <t>Rp514.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>32</v>
       </c>
       <c r="D60" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5617,16 +5617,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.900.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.266.000</t>
+          <t>Rp6.446.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp7.550.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5894,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.525.000</t>
+          <t>Rp21.670.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.850.000</t>
+          <t>Rp12.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp39.200.000</t>
+          <t>Rp41.550.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6188,28 +6188,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sweat and Social Padel (Arcici Sport Center)</t>
+          <t>Padel Green Pramuka City</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.140.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rp180.000 - Rp300.000</t>
+          <t>Rp250.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -6219,28 +6219,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bara Padel Court</t>
+          <t>Sweat and Social Padel (Arcici Sport Center)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.630.000</t>
+          <t>Rp3.140.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rp119.000 - Rp325.000</t>
+          <t>Rp180.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -6250,28 +6250,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Royal Padel</t>
+          <t>Bara Padel Court</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.705.000</t>
+          <t>Rp2.630.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp235.000 - Rp335.000</t>
+          <t>Rp119.000 - Rp325.000</t>
         </is>
       </c>
     </row>
@@ -6281,28 +6281,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Space Padel</t>
+          <t>Royal Padel</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp7.705.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rp180.000</t>
+          <t>Rp235.000 - Rp335.000</t>
         </is>
       </c>
     </row>
@@ -6312,28 +6312,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Padelyuk</t>
+          <t>The Space Padel</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rp175.000 - Rp300.000</t>
+          <t>Rp180.000</t>
         </is>
       </c>
     </row>
@@ -6343,28 +6343,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KOTA COURTS by PADELGRID Mangga Besar</t>
+          <t>Padelyuk</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.370.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp285.000</t>
+          <t>Rp175.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -6374,28 +6374,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Padel Wise Club</t>
+          <t>KOTA COURTS by PADELGRID Mangga Besar</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.045.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rp85.000 - Rp550.000</t>
+          <t>Rp100.000 - Rp285.000</t>
         </is>
       </c>
     </row>
@@ -6405,28 +6405,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AbsoluteFit Padel</t>
+          <t>Padel Wise Club</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp7.595.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp85.000 - Rp550.000</t>
         </is>
       </c>
     </row>
@@ -6436,28 +6436,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BBS PADEL</t>
+          <t>AbsoluteFit Padel</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -6467,28 +6467,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gru Padel House</t>
+          <t>BBS PADEL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp684.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rp168.000 - Rp228.000</t>
+          <t>Rp75.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -6498,26 +6498,57 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>Gru Padel House</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Rp684.000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rp168.000 - Rp228.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>JW COURT PADEL</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>64</v>
       </c>
-      <c r="D20" t="n">
-        <v>55</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>14.1%</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Rp5.291.000</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="D21" t="n">
+        <v>54</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rp5.790.000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>Rp399.000 - Rp999.000</t>
         </is>
@@ -6587,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.830.000</t>
+          <t>Rp9.810.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6618,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.160.000</t>
+          <t>Rp6.410.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6649,16 +6680,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.765.000</t>
+          <t>Rp11.365.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6680,16 +6711,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp207.000</t>
+          <t>Rp414.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6804,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.372.000</t>
+          <t>Rp8.722.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6928,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.626.000</t>
+          <t>Rp3.184.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7021,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.975.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7052,16 +7083,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7145,16 +7176,16 @@
         <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7247,7 +7278,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.303.000</t>
+          <t>Rp6.397.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7424,16 +7455,16 @@
         <v>85</v>
       </c>
       <c r="D29" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7486,16 +7517,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.279.000</t>
+          <t>Rp4.477.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7579,16 +7610,16 @@
         <v>108</v>
       </c>
       <c r="D34" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp9.290.000</t>
+          <t>Rp10.270.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7610,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp17.650.000</t>
+          <t>Rp18.750.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7703,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7703,16 +7734,16 @@
         <v>170</v>
       </c>
       <c r="D38" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7796,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp28.825.000</t>
+          <t>Rp29.525.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7827,16 +7858,16 @@
         <v>112</v>
       </c>
       <c r="D42" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp4.700.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8013,16 +8044,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.190.000</t>
+          <t>Rp7.590.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8044,16 +8075,16 @@
         <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8106,16 +8137,16 @@
         <v>98</v>
       </c>
       <c r="D51" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.260.000</t>
+          <t>Rp5.930.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8137,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.925.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8168,16 +8199,16 @@
         <v>90</v>
       </c>
       <c r="D53" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8281,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.760.000</t>
+          <t>Rp11.885.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8312,16 +8343,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.260.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8498,16 +8529,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.410.000</t>
+          <t>Rp2.740.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8560,16 +8591,16 @@
         <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8622,16 +8653,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.449.989</t>
+          <t>Rp5.149.988</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8653,16 +8684,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8684,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8715,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.290.000</t>
+          <t>Rp7.580.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8777,16 +8808,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp3.870.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8808,16 +8839,16 @@
         <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp20.730.000</t>
+          <t>Rp21.130.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8839,16 +8870,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp420.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8901,16 +8932,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.745.000</t>
+          <t>Rp8.160.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8994,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -9056,16 +9087,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.035.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9087,16 +9118,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9149,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9194,7 +9225,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp300.000</t>
+          <t>Rp150.000 - Rp282.000</t>
         </is>
       </c>
     </row>
@@ -9211,16 +9242,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp3.580.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9282,7 +9313,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.055.000</t>
+          <t>Rp5.253.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9366,16 +9397,16 @@
         <v>54</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.745.000</t>
+          <t>Rp4.495.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-23.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-23.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.360.000</t>
+          <t>Rp2.440.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>162</v>
       </c>
       <c r="D14" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.890.000</t>
+          <t>Rp15.046.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.720.000</t>
+          <t>Rp3.040.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.415.000</t>
+          <t>Rp5.795.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.910.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.160.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>112</v>
       </c>
       <c r="D98" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp3.330.000</t>
+          <t>Rp3.530.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp972.000</t>
+          <t>Rp1.053.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.163.500</t>
+          <t>Rp15.448.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.125.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.349.000</t>
+          <t>Rp1.749.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp23.700.000</t>
+          <t>Rp24.900.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp7.125.000</t>
+          <t>Rp5.625.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>72</v>
       </c>
       <c r="D54" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>45</v>
       </c>
       <c r="D61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.446.000</t>
+          <t>Rp6.596.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5803,16 +5803,16 @@
         <v>30</v>
       </c>
       <c r="D71" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp2.190.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5865,16 +5865,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp21.670.000</t>
+          <t>Rp22.550.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.150.000</t>
+          <t>Rp12.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp41.550.000</t>
+          <t>Rp41.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.630.000</t>
+          <t>Rp3.280.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6381,16 +6381,16 @@
         <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.370.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.810.000</t>
+          <t>Rp9.730.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.184.000</t>
+          <t>Rp3.742.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>96</v>
       </c>
       <c r="D32" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.265.000</t>
+          <t>Rp1.835.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.750.000</t>
+          <t>Rp18.800.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>84</v>
       </c>
       <c r="D37" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp1.710.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.228.000</t>
+          <t>Rp1.804.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>150</v>
       </c>
       <c r="D41" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp29.525.000</t>
+          <t>Rp30.225.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>80</v>
       </c>
       <c r="D43" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7951,16 +7951,16 @@
         <v>112</v>
       </c>
       <c r="D45" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp10.645.000</t>
+          <t>Rp10.755.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8044,16 +8044,16 @@
         <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.590.000</t>
+          <t>Rp7.990.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp3.020.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.870.000</t>
+          <t>Rp2.945.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp2.205.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp8.160.000</t>
+          <t>Rp8.355.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.017.000</t>
+          <t>Rp1.415.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -9428,16 +9428,16 @@
         <v>64</v>
       </c>
       <c r="D39" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.940.000</t>
+          <t>Rp2.278.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-23.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-23.xlsx
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1378,14 +1378,14 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp180.000</t>
+          <t>Rp35.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.795.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>72</v>
       </c>
       <c r="D44" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp10.420.000</t>
+          <t>Rp11.520.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>198</v>
       </c>
       <c r="D45" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp4.325.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>45</v>
       </c>
       <c r="D47" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.525.000</t>
+          <t>Rp1.675.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.184.000</t>
+          <t>Rp5.472.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.431.000</t>
+          <t>Rp6.131.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.525.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>90</v>
       </c>
       <c r="D74" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp3.925.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.053.000</t>
+          <t>Rp1.134.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.749.000</t>
+          <t>Rp1.949.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp7.575.000</t>
+          <t>Rp7.725.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.020.000</t>
+          <t>Rp2.205.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>234</v>
       </c>
       <c r="D67" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.596.000</t>
+          <t>Rp6.684.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.935.000</t>
+          <t>Rp9.285.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.500.000</t>
+          <t>Rp12.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.140.000</t>
+          <t>Rp2.640.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp9.730.000</t>
+          <t>Rp9.890.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.410.000</t>
+          <t>Rp8.360.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.722.000</t>
+          <t>Rp9.142.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.400.000</t>
+          <t>Rp23.000.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.397.000</t>
+          <t>Rp6.478.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>90</v>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.180.000</t>
+          <t>Rp6.330.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp6.960.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>187</v>
       </c>
       <c r="D35" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp18.800.000</t>
+          <t>Rp19.050.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>67</v>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.436.000</t>
+          <t>Rp5.624.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8168,16 +8168,16 @@
         <v>144</v>
       </c>
       <c r="D52" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.885.000</t>
+          <t>Rp12.345.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>108</v>
       </c>
       <c r="D10" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.020.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>36</v>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.745.000</t>
+          <t>Rp3.895.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
